--- a/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MI_PERU</t>
+          <t>MI PERU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>FERMIN AVILA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.855</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.1238</v>
-      </c>
-      <c r="I2" t="n">
-        <v>498</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.855</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.1238</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>5098 KUMAMOTO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.860933</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.127914</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1927</v>
-      </c>
-      <c r="J3" t="n">
-        <v>70</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.860933</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.127914</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>MANUEL SEOANE CORRALES</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.855265</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.121786</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2865</v>
-      </c>
-      <c r="J4" t="n">
-        <v>101</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.855265</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.121786</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2865</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>5119 VILLA EMILIA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.850188</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.12137199999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>667</v>
-      </c>
-      <c r="J5" t="n">
-        <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.850188</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.121372</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>SAN JUAN</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.853735</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.12652</v>
-      </c>
-      <c r="I6" t="n">
-        <v>391</v>
-      </c>
-      <c r="J6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.853735</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.12652</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>ELIM</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.853999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.123127</v>
-      </c>
-      <c r="I7" t="n">
-        <v>629</v>
-      </c>
-      <c r="J7" t="n">
-        <v>33</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.853999</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.123127</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>FE Y ALEGRIA 33</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.856869</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.121139</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1630</v>
-      </c>
-      <c r="J8" t="n">
-        <v>72</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.856869</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.121139</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.859625</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.126417</v>
-      </c>
-      <c r="I9" t="n">
-        <v>116</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.859625</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.126417</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>CIRO ALEGRIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.853405</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.126357</v>
-      </c>
-      <c r="I10" t="n">
-        <v>201</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.853405</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.126357</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>5151 SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.850549</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.126329</v>
-      </c>
-      <c r="I11" t="n">
-        <v>504</v>
-      </c>
-      <c r="J11" t="n">
-        <v>22</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.850549</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.126329</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>5130-4 / 5130-4 CHAVINILLO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.846896</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.115757</v>
-      </c>
-      <c r="I12" t="n">
-        <v>542</v>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.846896</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.115757</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>5135 LA SALLE</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.846952</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.114048</v>
-      </c>
-      <c r="I13" t="n">
-        <v>874</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.846952</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.114048</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>SAN JOSE DE VIGNY</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.857512</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.126029</v>
-      </c>
-      <c r="I14" t="n">
-        <v>54</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.857512</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.126029</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>GENIUS KIDS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.85952</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.12782</v>
-      </c>
-      <c r="I15" t="n">
-        <v>221</v>
-      </c>
-      <c r="J15" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.85952</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.12782</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>161</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.857815</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.12652</v>
-      </c>
-      <c r="I16" t="n">
-        <v>240</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.857815</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.12652</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>167 CRISTO REY DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.850058</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.122489</v>
-      </c>
-      <c r="I17" t="n">
-        <v>240</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.850058</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.122489</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>ESTACION ESPERANZA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.855356</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.123591</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.855356</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.123591</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>144490</t>
+          <t>911891</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FERMIN AVILA</t>
+          <t>ESTACION ESPERANZA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.855</t>
+          <t>-11.855356</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.1238</t>
+          <t>-77.123591</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>144659</t>
+          <t>787349</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5098 KUMAMOTO</t>
+          <t>167 CRISTO REY DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.860933</t>
+          <t>-11.850058</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.127914</t>
+          <t>-77.122489</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>144763</t>
+          <t>650695</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5119 VILLA EMILIA</t>
+          <t>GENIUS KIDS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.850188</t>
+          <t>-11.85952</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.121372</t>
+          <t>-77.12782</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>144923</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>CIRO ALEGRIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.853735</t>
+          <t>-11.853405</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.12652</t>
+          <t>-77.126357</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>145135</t>
+          <t>144490</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ELIM</t>
+          <t>FERMIN AVILA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.853999</t>
+          <t>-11.855</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.123127</t>
+          <t>-77.1238</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>498</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>145244</t>
+          <t>144923</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 33</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.856869</t>
+          <t>-11.853735</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.121139</t>
+          <t>-77.12652</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>145324</t>
+          <t>514014</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>5151 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.859625</t>
+          <t>-11.850549</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.126417</t>
+          <t>-77.126329</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>145480</t>
+          <t>144763</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CIRO ALEGRIA</t>
+          <t>5119 VILLA EMILIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.853405</t>
+          <t>-11.850188</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.126357</t>
+          <t>-77.121372</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>514014</t>
+          <t>594039</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5151 SAN JUAN BOSCO</t>
+          <t>5130-4 / 5130-4 CHAVINILLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.850549</t>
+          <t>-11.846896</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.126329</t>
+          <t>-77.115757</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>542</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>594039</t>
+          <t>145135</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5130-4 / 5130-4 CHAVINILLO</t>
+          <t>ELIM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.846896</t>
+          <t>-11.853999</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.115757</t>
+          <t>-77.123127</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>629</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>650695</t>
+          <t>145324</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GENIUS KIDS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.85952</t>
+          <t>-11.859625</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.12782</t>
+          <t>-77.126417</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>678878</t>
+          <t>144659</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>5098 KUMAMOTO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.857815</t>
+          <t>-11.860933</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.12652</t>
+          <t>-77.127914</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>787349</t>
+          <t>145244</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>167 CRISTO REY DE LOS NIÑOS</t>
+          <t>FE Y ALEGRIA 33</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.850058</t>
+          <t>-11.856869</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.122489</t>
+          <t>-77.121139</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>911891</t>
+          <t>678878</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ESTACION ESPERANZA</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.855356</t>
+          <t>-11.857815</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.123591</t>
+          <t>-77.12652</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
@@ -511,22 +511,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-11.855356</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-77.123591</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>-11.850058</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-77.122489</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>144683</t>
+          <t>678878</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MANUEL SEOANE CORRALES</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.855265</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.121786</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>-11.857815</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>-77.12652</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>-11.85952</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-77.12782</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>145480</t>
+          <t>595675</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CIRO ALEGRIA</t>
+          <t>SAN JOSE DE VIGNY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.853405</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.126357</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-11.857512</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.126029</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>144490</t>
+          <t>594143</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FERMIN AVILA</t>
+          <t>5135 LA SALLE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.855</t>
+          <t>874</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.1238</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>-11.846952</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.114048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>144923</t>
+          <t>594039</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>5130-4 / 5130-4 CHAVINILLO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.853735</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.12652</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-11.846896</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.115757</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -945,22 +945,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>-11.850549</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>-77.126329</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>144763</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5119 VILLA EMILIA</t>
+          <t>CIRO ALEGRIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.850188</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.121372</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>-11.853405</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.126357</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>594039</t>
+          <t>145324</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5130-4 / 5130-4 CHAVINILLO</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.846896</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.115757</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>-11.859625</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.126417</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>145135</t>
+          <t>145244</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ELIM</t>
+          <t>FE Y ALEGRIA 33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.853999</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.123127</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>-11.856869</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.121139</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>594143</t>
+          <t>145135</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5135 LA SALLE</t>
+          <t>ELIM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.846952</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.114048</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>-11.853999</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.123127</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>595675</t>
+          <t>144923</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN JOSE DE VIGNY</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.857512</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.126029</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-11.853735</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.12652</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>145324</t>
+          <t>144763</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>5119 VILLA EMILIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.859625</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.126417</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-11.850188</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-77.121372</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>144659</t>
+          <t>144683</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5098 KUMAMOTO</t>
+          <t>MANUEL SEOANE CORRALES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.860933</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.127914</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>-11.855265</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-77.121786</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>145244</t>
+          <t>144659</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 33</t>
+          <t>5098 KUMAMOTO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.856869</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.121139</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>-11.860933</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-77.127914</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>678878</t>
+          <t>144490</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>FERMIN AVILA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.857815</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.12652</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-11.855</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.1238</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-MI_PERU.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
